--- a/data/partidos.xlsx
+++ b/data/partidos.xlsx
@@ -1,74 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381B1B8B-82E2-4959-8BB9-9F99B3050881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="8160" yWindow="4650" windowWidth="18015" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>fecha</t>
-  </si>
-  <si>
-    <t>equipo1</t>
-  </si>
-  <si>
-    <t>equipo2</t>
-  </si>
-  <si>
-    <t>goles1</t>
-  </si>
-  <si>
-    <t>goles2</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -86,24 +46,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -118,44 +135,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -182,15 +199,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -217,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -229,172 +244,225 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>equipos1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>equipos2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>goles1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>goles2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>11/11/2011</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/partidos.xlsx
+++ b/data/partidos.xlsx
@@ -1,34 +1,78 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4EB364-28F7-4DEC-8034-D8F56DEB5024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="5535" yWindow="9750" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>goles1</t>
+  </si>
+  <si>
+    <t>goles2</t>
+  </si>
+  <si>
+    <t>hora</t>
+  </si>
+  <si>
+    <t>lugar</t>
+  </si>
+  <si>
+    <t>equipo1</t>
+  </si>
+  <si>
+    <t>equipo2</t>
+  </si>
+  <si>
+    <t>penales1</t>
+  </si>
+  <si>
+    <t>penales2</t>
+  </si>
+  <si>
+    <t>fase</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +91,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,58 +393,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>fecha</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>equipos1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>equipos2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>goles1</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>goles2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>11/11/2011</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/partidos.xlsx
+++ b/data/partidos.xlsx
@@ -1,78 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4EB364-28F7-4DEC-8034-D8F56DEB5024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="5535" yWindow="9750" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>fecha</t>
-  </si>
-  <si>
-    <t>goles1</t>
-  </si>
-  <si>
-    <t>goles2</t>
-  </si>
-  <si>
-    <t>hora</t>
-  </si>
-  <si>
-    <t>lugar</t>
-  </si>
-  <si>
-    <t>equipo1</t>
-  </si>
-  <si>
-    <t>equipo2</t>
-  </si>
-  <si>
-    <t>penales1</t>
-  </si>
-  <si>
-    <t>penales2</t>
-  </si>
-  <si>
-    <t>fase</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -91,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -393,40 +408,108 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>hora</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lugar</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>equipo1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>equipo2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>goles1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>goles2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>penales1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>penales2</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>fase</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>a confirmar</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Grupos</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/partidos.xlsx
+++ b/data/partidos.xlsx
@@ -481,24 +481,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>a confirmar</t>
+          <t>Estadio el pepe</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>

--- a/data/partidos.xlsx
+++ b/data/partidos.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B5547A-7202-4208-B9FE-157843898B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="1365" yWindow="9420" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -20,88 +28,73 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t xml:space="preserve">fecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lugar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">equipo1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">equipo2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goles1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goles2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penales1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penales2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jugado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estadio el pepe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grupos</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>hora</t>
+  </si>
+  <si>
+    <t>lugar</t>
+  </si>
+  <si>
+    <t>equipo1</t>
+  </si>
+  <si>
+    <t>equipo2</t>
+  </si>
+  <si>
+    <t>goles1</t>
+  </si>
+  <si>
+    <t>goles2</t>
+  </si>
+  <si>
+    <t>penales1</t>
+  </si>
+  <si>
+    <t>penales2</t>
+  </si>
+  <si>
+    <t>fase</t>
+  </si>
+  <si>
+    <t>jugado</t>
+  </si>
+  <si>
+    <t>11/06/2026</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>Estadio el pepe</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Grupos</t>
+  </si>
+  <si>
+    <t>id_partido</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -113,7 +106,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -121,50 +114,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -206,12 +179,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -240,7 +213,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -261,7 +234,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -312,7 +285,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -330,102 +303,100 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.02"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="0" t="s">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/data/partidos.xlsx
+++ b/data/partidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B5547A-7202-4208-B9FE-157843898B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECC56B8-77E8-401F-B8FF-2B75460D48D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1365" yWindow="9420" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1365" yWindow="4185" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>fecha</t>
   </si>
@@ -61,24 +61,6 @@
   </si>
   <si>
     <t>jugado</t>
-  </si>
-  <si>
-    <t>11/06/2026</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>Estadio el pepe</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>Grupos</t>
   </si>
   <si>
     <t>id_partido</t>
@@ -315,7 +297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="18" customWidth="1"/>
@@ -357,42 +339,7 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
         <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/partidos.xlsx
+++ b/data/partidos.xlsx
@@ -8,20 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECC56B8-77E8-401F-B8FF-2B75460D48D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC83C4A-C643-4B84-80B7-BEB496B7BBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1365" yWindow="4185" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13680" yWindow="2580" windowWidth="14490" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -76,7 +73,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -106,7 +103,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -123,10 +120,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -164,128 +161,234 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -298,10 +401,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -343,7 +445,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/partidos.xlsx
+++ b/data/partidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58280E4-55B1-4FF8-8876-9177DCA96BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C91E699-0A6C-417C-A622-DCAFE204EC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="3750" windowWidth="14490" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7665" yWindow="2100" windowWidth="17505" windowHeight="13380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="127">
   <si>
     <t>fecha</t>
   </si>
@@ -61,12 +61,360 @@
   </si>
   <si>
     <t>id_partido</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>Estadio Azteca, Ciudad de México</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Grupos</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>Estadio BBVA, Monterrey</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>BC Place, Vancouver</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>MetLife Stadium, East Rutherford</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Hard Rock Stadium, Miami</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>Maracaná, Río de Janeiro</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz Stadium, Atlanta</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>SoFi Stadium, Los Angeles</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>AT&amp;T Stadium, Dallas</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>Arrowhead Stadium, Kansas City</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>NRG Stadium, Houston</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>Lincoln Financial Field, Philadelphia</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>Lumen Field, Seattle</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>Gillette Stadium, Boston</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>BMO Field, Toronto</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>Estadio Akron, Guadalajara</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>I1</t>
+  </si>
+  <si>
+    <t>I2</t>
+  </si>
+  <si>
+    <t>I3</t>
+  </si>
+  <si>
+    <t>I4</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>K1</t>
+  </si>
+  <si>
+    <t>K2</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>K3</t>
+  </si>
+  <si>
+    <t>K4</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>Dieciseisavos</t>
+  </si>
+  <si>
+    <t>M73</t>
+  </si>
+  <si>
+    <t>M74</t>
+  </si>
+  <si>
+    <t>M75</t>
+  </si>
+  <si>
+    <t>M76</t>
+  </si>
+  <si>
+    <t>M77</t>
+  </si>
+  <si>
+    <t>M78</t>
+  </si>
+  <si>
+    <t>M79</t>
+  </si>
+  <si>
+    <t>M80</t>
+  </si>
+  <si>
+    <t>M81</t>
+  </si>
+  <si>
+    <t>M82</t>
+  </si>
+  <si>
+    <t>M83</t>
+  </si>
+  <si>
+    <t>M84</t>
+  </si>
+  <si>
+    <t>M85</t>
+  </si>
+  <si>
+    <t>M86</t>
+  </si>
+  <si>
+    <t>M87</t>
+  </si>
+  <si>
+    <t>M88</t>
+  </si>
+  <si>
+    <t>Octavos</t>
+  </si>
+  <si>
+    <t>M89</t>
+  </si>
+  <si>
+    <t>M90</t>
+  </si>
+  <si>
+    <t>M91</t>
+  </si>
+  <si>
+    <t>M92</t>
+  </si>
+  <si>
+    <t>M93</t>
+  </si>
+  <si>
+    <t>M94</t>
+  </si>
+  <si>
+    <t>M95</t>
+  </si>
+  <si>
+    <t>M96</t>
+  </si>
+  <si>
+    <t>Cuartos</t>
+  </si>
+  <si>
+    <t>M97</t>
+  </si>
+  <si>
+    <t>M98</t>
+  </si>
+  <si>
+    <t>M99</t>
+  </si>
+  <si>
+    <t>M100</t>
+  </si>
+  <si>
+    <t>Semifinal</t>
+  </si>
+  <si>
+    <t>M101</t>
+  </si>
+  <si>
+    <t>M102</t>
+  </si>
+  <si>
+    <t>Tercer Puesto</t>
+  </si>
+  <si>
+    <t>M103</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>M104</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -96,8 +444,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,14 +749,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" customWidth="1"/>
-    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -445,6 +788,3646 @@
       </c>
       <c r="L1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28" t="s">
+        <v>16</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29" t="s">
+        <v>16</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34">
+        <v>4</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35" t="s">
+        <v>16</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B36" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36" t="s">
+        <v>16</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37">
+        <v>3</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37" t="s">
+        <v>16</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38" t="s">
+        <v>16</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39">
+        <v>3</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39" t="s">
+        <v>16</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B40" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40" t="s">
+        <v>16</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" t="s">
+        <v>63</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41" t="s">
+        <v>16</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" t="s">
+        <v>74</v>
+      </c>
+      <c r="E42" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42" t="s">
+        <v>16</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B43" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" t="s">
+        <v>70</v>
+      </c>
+      <c r="E43" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" t="s">
+        <v>16</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44" t="s">
+        <v>16</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" t="s">
+        <v>75</v>
+      </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
+      <c r="G45">
+        <v>2</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" t="s">
+        <v>78</v>
+      </c>
+      <c r="E46" t="s">
+        <v>84</v>
+      </c>
+      <c r="F46">
+        <v>4</v>
+      </c>
+      <c r="G46">
+        <v>2</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46" t="s">
+        <v>16</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" t="s">
+        <v>61</v>
+      </c>
+      <c r="D47" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" t="s">
+        <v>82</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47" t="s">
+        <v>16</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48">
+        <v>3</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" t="s">
+        <v>85</v>
+      </c>
+      <c r="E49" t="s">
+        <v>79</v>
+      </c>
+      <c r="F49">
+        <v>4</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49" t="s">
+        <v>16</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50" t="s">
+        <v>16</v>
+      </c>
+      <c r="K50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>3</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51" t="s">
+        <v>16</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B52" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" t="s">
+        <v>33</v>
+      </c>
+      <c r="E52" t="s">
+        <v>37</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>4</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52" t="s">
+        <v>16</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" t="s">
+        <v>34</v>
+      </c>
+      <c r="E53" t="s">
+        <v>36</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53" t="s">
+        <v>16</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54">
+        <v>4</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54" t="s">
+        <v>16</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>4</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55" t="s">
+        <v>16</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B56" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" t="s">
+        <v>53</v>
+      </c>
+      <c r="E56" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56">
+        <v>4</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
+        <v>16</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B57" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" t="s">
+        <v>52</v>
+      </c>
+      <c r="F57">
+        <v>4</v>
+      </c>
+      <c r="G57">
+        <v>3</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57" t="s">
+        <v>16</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B58" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58" t="s">
+        <v>55</v>
+      </c>
+      <c r="E58" t="s">
+        <v>48</v>
+      </c>
+      <c r="F58">
+        <v>4</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58" t="s">
+        <v>16</v>
+      </c>
+      <c r="K58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B59" t="s">
+        <v>50</v>
+      </c>
+      <c r="C59" t="s">
+        <v>47</v>
+      </c>
+      <c r="D59" t="s">
+        <v>49</v>
+      </c>
+      <c r="E59" t="s">
+        <v>56</v>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59">
+        <v>3</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59" t="s">
+        <v>16</v>
+      </c>
+      <c r="K59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D60" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" t="s">
+        <v>41</v>
+      </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+      <c r="G60">
+        <v>2</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60" t="s">
+        <v>16</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" t="s">
+        <v>54</v>
+      </c>
+      <c r="D61" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" t="s">
+        <v>40</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61" t="s">
+        <v>16</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B62" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" t="s">
+        <v>58</v>
+      </c>
+      <c r="D62" t="s">
+        <v>73</v>
+      </c>
+      <c r="E62" t="s">
+        <v>70</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>3</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62" t="s">
+        <v>16</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" t="s">
+        <v>61</v>
+      </c>
+      <c r="D63" t="s">
+        <v>71</v>
+      </c>
+      <c r="E63" t="s">
+        <v>72</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63">
+        <v>3</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63" t="s">
+        <v>16</v>
+      </c>
+      <c r="K63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B64" t="s">
+        <v>86</v>
+      </c>
+      <c r="C64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D64" t="s">
+        <v>66</v>
+      </c>
+      <c r="E64" t="s">
+        <v>59</v>
+      </c>
+      <c r="F64">
+        <v>4</v>
+      </c>
+      <c r="G64">
+        <v>3</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64" t="s">
+        <v>16</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B65" t="s">
+        <v>86</v>
+      </c>
+      <c r="C65" t="s">
+        <v>67</v>
+      </c>
+      <c r="D65" t="s">
+        <v>60</v>
+      </c>
+      <c r="E65" t="s">
+        <v>65</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65" t="s">
+        <v>16</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B66" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" t="s">
+        <v>47</v>
+      </c>
+      <c r="D66" t="s">
+        <v>62</v>
+      </c>
+      <c r="E66" t="s">
+        <v>69</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" t="s">
+        <v>51</v>
+      </c>
+      <c r="D67" t="s">
+        <v>63</v>
+      </c>
+      <c r="E67" t="s">
+        <v>68</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67" t="s">
+        <v>16</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" t="s">
+        <v>25</v>
+      </c>
+      <c r="D68" t="s">
+        <v>74</v>
+      </c>
+      <c r="E68" t="s">
+        <v>77</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68" t="s">
+        <v>16</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B69" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" t="s">
+        <v>28</v>
+      </c>
+      <c r="D69" t="s">
+        <v>75</v>
+      </c>
+      <c r="E69" t="s">
+        <v>76</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69" t="s">
+        <v>16</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B70" t="s">
+        <v>46</v>
+      </c>
+      <c r="C70" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70" t="s">
+        <v>79</v>
+      </c>
+      <c r="E70" t="s">
+        <v>84</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70" t="s">
+        <v>16</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B71" t="s">
+        <v>46</v>
+      </c>
+      <c r="C71" t="s">
+        <v>43</v>
+      </c>
+      <c r="D71" t="s">
+        <v>85</v>
+      </c>
+      <c r="E71" t="s">
+        <v>78</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71" t="s">
+        <v>16</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C72" t="s">
+        <v>54</v>
+      </c>
+      <c r="D72" t="s">
+        <v>80</v>
+      </c>
+      <c r="E72" t="s">
+        <v>83</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72" t="s">
+        <v>16</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B73" t="s">
+        <v>86</v>
+      </c>
+      <c r="C73" t="s">
+        <v>58</v>
+      </c>
+      <c r="D73" t="s">
+        <v>81</v>
+      </c>
+      <c r="E73" t="s">
+        <v>82</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73" t="s">
+        <v>16</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B74" t="s">
+        <v>42</v>
+      </c>
+      <c r="C74" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" t="s">
+        <v>23</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74" t="s">
+        <v>89</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B75" t="s">
+        <v>46</v>
+      </c>
+      <c r="C75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D75" t="s">
+        <v>53</v>
+      </c>
+      <c r="E75" t="s">
+        <v>60</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75" t="s">
+        <v>89</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B76" t="s">
+        <v>50</v>
+      </c>
+      <c r="C76" t="s">
+        <v>43</v>
+      </c>
+      <c r="D76" t="s">
+        <v>55</v>
+      </c>
+      <c r="E76" t="s">
+        <v>37</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76" t="s">
+        <v>89</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" t="s">
+        <v>36</v>
+      </c>
+      <c r="E77" t="s">
+        <v>48</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77" t="s">
+        <v>89</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B78" t="s">
+        <v>42</v>
+      </c>
+      <c r="C78" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78" t="s">
+        <v>70</v>
+      </c>
+      <c r="E78" t="s">
+        <v>56</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78" t="s">
+        <v>89</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B79" t="s">
+        <v>46</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" t="s">
+        <v>72</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79" t="s">
+        <v>89</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B80" t="s">
+        <v>50</v>
+      </c>
+      <c r="C80" t="s">
+        <v>51</v>
+      </c>
+      <c r="D80" t="s">
+        <v>19</v>
+      </c>
+      <c r="E80" t="s">
+        <v>78</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80" t="s">
+        <v>89</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B81" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" t="s">
+        <v>47</v>
+      </c>
+      <c r="D81" t="s">
+        <v>83</v>
+      </c>
+      <c r="E81" t="s">
+        <v>34</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81" t="s">
+        <v>89</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B82" t="s">
+        <v>42</v>
+      </c>
+      <c r="C82" t="s">
+        <v>54</v>
+      </c>
+      <c r="D82" t="s">
+        <v>27</v>
+      </c>
+      <c r="E82" t="s">
+        <v>73</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82" t="s">
+        <v>89</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B83" t="s">
+        <v>46</v>
+      </c>
+      <c r="C83" t="s">
+        <v>58</v>
+      </c>
+      <c r="D83" t="s">
+        <v>63</v>
+      </c>
+      <c r="E83" t="s">
+        <v>69</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83" t="s">
+        <v>89</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B84" t="s">
+        <v>50</v>
+      </c>
+      <c r="C84" t="s">
+        <v>61</v>
+      </c>
+      <c r="D84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E84" t="s">
+        <v>80</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84" t="s">
+        <v>89</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B85" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" t="s">
+        <v>59</v>
+      </c>
+      <c r="E85" t="s">
+        <v>74</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85" t="s">
+        <v>89</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B86" t="s">
+        <v>42</v>
+      </c>
+      <c r="C86" t="s">
+        <v>64</v>
+      </c>
+      <c r="D86" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" t="s">
+        <v>77</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86" t="s">
+        <v>89</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B87" t="s">
+        <v>46</v>
+      </c>
+      <c r="C87" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" t="s">
+        <v>75</v>
+      </c>
+      <c r="E87" t="s">
+        <v>66</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87" t="s">
+        <v>89</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B88" t="s">
+        <v>50</v>
+      </c>
+      <c r="C88" t="s">
+        <v>67</v>
+      </c>
+      <c r="D88" t="s">
+        <v>84</v>
+      </c>
+      <c r="E88" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88" t="s">
+        <v>89</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" t="s">
+        <v>41</v>
+      </c>
+      <c r="E89" t="s">
+        <v>68</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89" t="s">
+        <v>89</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B90" t="s">
+        <v>46</v>
+      </c>
+      <c r="C90" t="s">
+        <v>28</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90" t="s">
+        <v>106</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B91" t="s">
+        <v>86</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91" t="s">
+        <v>106</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B92" t="s">
+        <v>46</v>
+      </c>
+      <c r="C92" t="s">
+        <v>51</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92" t="s">
+        <v>106</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B93" t="s">
+        <v>86</v>
+      </c>
+      <c r="C93" t="s">
+        <v>47</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93" t="s">
+        <v>106</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B94" t="s">
+        <v>46</v>
+      </c>
+      <c r="C94" t="s">
+        <v>54</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94" t="s">
+        <v>106</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B95" t="s">
+        <v>86</v>
+      </c>
+      <c r="C95" t="s">
+        <v>58</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95" t="s">
+        <v>106</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B96" t="s">
+        <v>46</v>
+      </c>
+      <c r="C96" t="s">
+        <v>61</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96" t="s">
+        <v>106</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B97" t="s">
+        <v>86</v>
+      </c>
+      <c r="C97" t="s">
+        <v>21</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97" t="s">
+        <v>106</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B98" t="s">
+        <v>46</v>
+      </c>
+      <c r="C98" t="s">
+        <v>54</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98" t="s">
+        <v>115</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B99" t="s">
+        <v>86</v>
+      </c>
+      <c r="C99" t="s">
+        <v>58</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99" t="s">
+        <v>115</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B100" t="s">
+        <v>46</v>
+      </c>
+      <c r="C100" t="s">
+        <v>61</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100" t="s">
+        <v>115</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B101" t="s">
+        <v>86</v>
+      </c>
+      <c r="C101" t="s">
+        <v>21</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101" t="s">
+        <v>115</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B102" t="s">
+        <v>86</v>
+      </c>
+      <c r="C102" t="s">
+        <v>43</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102" t="s">
+        <v>120</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B103" t="s">
+        <v>86</v>
+      </c>
+      <c r="C103" t="s">
+        <v>35</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103" t="s">
+        <v>120</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>46221</v>
+      </c>
+      <c r="B104" t="s">
+        <v>46</v>
+      </c>
+      <c r="C104" t="s">
+        <v>28</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104" t="s">
+        <v>123</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B105" t="s">
+        <v>87</v>
+      </c>
+      <c r="C105" t="s">
+        <v>25</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105" t="s">
+        <v>125</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
